--- a/uploads/saturday schedule.xlsx
+++ b/uploads/saturday schedule.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dev\GitHub\nso_schedules\uploads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B788E6F1-F4EF-4A6A-BAB7-C7BF22F83C6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC9A7F99-5E84-4513-92EA-E50C03C76081}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -845,23 +845,39 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1151,16 +1167,14 @@
   <dimension ref="A1:R87"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="23.1796875" customWidth="1"/>
-    <col min="2" max="3" width="16.54296875" customWidth="1"/>
-    <col min="16" max="16" width="11.7265625" customWidth="1"/>
+    <col min="1" max="18" width="13.36328125" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="101.5" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
@@ -1212,2446 +1226,2446 @@
         <v>122</v>
       </c>
     </row>
-    <row r="2" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="5" t="s">
+    <row r="2" spans="1:18" ht="87" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="B2">
+      <c r="B2" s="1">
         <v>1</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="E2" t="s">
-        <v>74</v>
-      </c>
-      <c r="G2" t="s">
-        <v>73</v>
-      </c>
-      <c r="H2" t="s">
-        <v>89</v>
-      </c>
-      <c r="I2" t="s">
-        <v>99</v>
-      </c>
-      <c r="K2" t="s">
+      <c r="E2" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="K2" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="O2" t="s">
+      <c r="O2" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="P2" t="s">
+      <c r="P2" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="R2" t="s">
+      <c r="R2" s="1" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="3" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="5" t="s">
+    <row r="3" spans="1:18" ht="87" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B3">
+      <c r="B3" s="1">
         <v>1</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D3" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="E3" t="s">
-        <v>74</v>
-      </c>
-      <c r="G3" t="s">
-        <v>73</v>
-      </c>
-      <c r="H3" t="s">
-        <v>89</v>
-      </c>
-      <c r="I3" t="s">
-        <v>99</v>
-      </c>
-      <c r="K3" t="s">
+      <c r="E3" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="K3" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="O3" t="s">
+      <c r="O3" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="P3" t="s">
+      <c r="P3" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="R3" t="s">
+      <c r="R3" s="1" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="4" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="5" t="s">
+    <row r="4" spans="1:18" ht="87" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="B4">
+      <c r="B4" s="1">
         <v>15</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D4" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="E4" t="s">
-        <v>74</v>
-      </c>
-      <c r="G4" t="s">
-        <v>73</v>
-      </c>
-      <c r="H4" t="s">
-        <v>89</v>
-      </c>
-      <c r="I4" t="s">
-        <v>99</v>
-      </c>
-      <c r="K4" t="s">
+      <c r="E4" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="K4" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="O4" t="s">
+      <c r="O4" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="P4" t="s">
+      <c r="P4" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="R4" t="s">
+      <c r="R4" s="1" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="5" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="5" t="s">
+    <row r="5" spans="1:18" ht="87" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B5">
+      <c r="B5" s="1">
         <v>15</v>
       </c>
-      <c r="D5" t="s">
+      <c r="D5" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="E5" t="s">
-        <v>74</v>
-      </c>
-      <c r="G5" t="s">
-        <v>73</v>
-      </c>
-      <c r="H5" t="s">
-        <v>89</v>
-      </c>
-      <c r="I5" t="s">
-        <v>99</v>
-      </c>
-      <c r="K5" t="s">
+      <c r="E5" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="K5" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="O5" t="s">
+      <c r="O5" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="P5" t="s">
+      <c r="P5" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="R5" t="s">
+      <c r="R5" s="1" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="6" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="5" t="s">
+    <row r="6" spans="1:18" ht="87" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="B6">
+      <c r="B6" s="1">
         <v>3</v>
       </c>
-      <c r="D6" t="s">
+      <c r="D6" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="E6" t="s">
-        <v>74</v>
-      </c>
-      <c r="G6" t="s">
-        <v>73</v>
-      </c>
-      <c r="H6" t="s">
-        <v>89</v>
-      </c>
-      <c r="I6" t="s">
-        <v>99</v>
-      </c>
-      <c r="K6" t="s">
+      <c r="E6" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="K6" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="O6" t="s">
+      <c r="O6" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="P6" t="s">
+      <c r="P6" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="R6" t="s">
+      <c r="R6" s="1" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="7" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="5" t="s">
+    <row r="7" spans="1:18" ht="87" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="B7">
+      <c r="B7" s="1">
         <v>3</v>
       </c>
-      <c r="D7" t="s">
+      <c r="D7" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="E7" t="s">
-        <v>74</v>
-      </c>
-      <c r="G7" t="s">
-        <v>73</v>
-      </c>
-      <c r="H7" t="s">
-        <v>89</v>
-      </c>
-      <c r="I7" t="s">
-        <v>99</v>
-      </c>
-      <c r="K7" t="s">
+      <c r="E7" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="K7" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="O7" t="s">
+      <c r="O7" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="P7" t="s">
+      <c r="P7" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="R7" t="s">
+      <c r="R7" s="1" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="8" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="5" t="s">
+    <row r="8" spans="1:18" ht="87" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="B8">
+      <c r="B8" s="1">
         <v>2</v>
       </c>
-      <c r="D8" t="s">
+      <c r="D8" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="E8" t="s">
-        <v>74</v>
-      </c>
-      <c r="G8" t="s">
-        <v>73</v>
-      </c>
-      <c r="H8" t="s">
-        <v>89</v>
-      </c>
-      <c r="I8" t="s">
-        <v>99</v>
-      </c>
-      <c r="K8" t="s">
+      <c r="E8" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="I8" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="K8" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="O8" t="s">
+      <c r="O8" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="P8" t="s">
+      <c r="P8" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="R8" t="s">
+      <c r="R8" s="1" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="9" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="5" t="s">
+    <row r="9" spans="1:18" ht="87" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="B9">
+      <c r="B9" s="1">
         <v>2</v>
       </c>
-      <c r="D9" t="s">
+      <c r="D9" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="E9" t="s">
-        <v>74</v>
-      </c>
-      <c r="G9" t="s">
-        <v>73</v>
-      </c>
-      <c r="H9" t="s">
-        <v>89</v>
-      </c>
-      <c r="I9" t="s">
-        <v>99</v>
-      </c>
-      <c r="K9" t="s">
+      <c r="E9" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="I9" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="K9" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="O9" t="s">
+      <c r="O9" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="P9" t="s">
+      <c r="P9" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="R9" t="s">
+      <c r="R9" s="1" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="10" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="5" t="s">
+    <row r="10" spans="1:18" ht="87" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="B10">
+      <c r="B10" s="1">
         <v>13</v>
       </c>
-      <c r="D10" t="s">
+      <c r="D10" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="E10" t="s">
-        <v>74</v>
-      </c>
-      <c r="G10" t="s">
-        <v>73</v>
-      </c>
-      <c r="H10" t="s">
-        <v>89</v>
-      </c>
-      <c r="I10" t="s">
-        <v>99</v>
-      </c>
-      <c r="K10" t="s">
+      <c r="E10" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="I10" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="K10" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="O10" t="s">
+      <c r="O10" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="P10" t="s">
+      <c r="P10" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="R10" t="s">
+      <c r="R10" s="1" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="11" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="5" t="s">
+    <row r="11" spans="1:18" ht="87" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="B11">
+      <c r="B11" s="1">
         <v>13</v>
       </c>
-      <c r="D11" t="s">
+      <c r="D11" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="E11" t="s">
-        <v>74</v>
-      </c>
-      <c r="G11" t="s">
-        <v>73</v>
-      </c>
-      <c r="H11" t="s">
-        <v>89</v>
-      </c>
-      <c r="I11" t="s">
-        <v>99</v>
-      </c>
-      <c r="K11" t="s">
+      <c r="E11" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="H11" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="I11" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="K11" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="O11" t="s">
+      <c r="O11" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="P11" t="s">
+      <c r="P11" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="R11" t="s">
+      <c r="R11" s="1" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="12" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="5" t="s">
+    <row r="12" spans="1:18" ht="87" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B12">
+      <c r="B12" s="1">
         <v>4</v>
       </c>
-      <c r="D12" t="s">
+      <c r="D12" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="E12" t="s">
-        <v>74</v>
-      </c>
-      <c r="G12" t="s">
-        <v>73</v>
-      </c>
-      <c r="H12" t="s">
-        <v>89</v>
-      </c>
-      <c r="I12" t="s">
-        <v>99</v>
-      </c>
-      <c r="K12" t="s">
+      <c r="E12" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="H12" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="I12" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="K12" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="O12" t="s">
+      <c r="O12" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="P12" t="s">
+      <c r="P12" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="R12" t="s">
+      <c r="R12" s="1" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="13" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="5" t="s">
+    <row r="13" spans="1:18" ht="87" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="B13">
+      <c r="B13" s="1">
         <v>4</v>
       </c>
-      <c r="D13" t="s">
+      <c r="D13" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="E13" t="s">
-        <v>74</v>
-      </c>
-      <c r="G13" t="s">
-        <v>73</v>
-      </c>
-      <c r="H13" t="s">
-        <v>89</v>
-      </c>
-      <c r="I13" t="s">
-        <v>99</v>
-      </c>
-      <c r="K13" t="s">
+      <c r="E13" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="H13" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="I13" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="K13" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="O13" t="s">
+      <c r="O13" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="P13" t="s">
+      <c r="P13" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="R13" t="s">
+      <c r="R13" s="1" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="14" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="5" t="s">
+    <row r="14" spans="1:18" ht="87" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B14">
+      <c r="B14" s="1">
         <v>16</v>
       </c>
-      <c r="D14" t="s">
+      <c r="D14" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="E14" t="s">
-        <v>74</v>
-      </c>
-      <c r="G14" t="s">
-        <v>73</v>
-      </c>
-      <c r="H14" t="s">
-        <v>89</v>
-      </c>
-      <c r="I14" t="s">
-        <v>99</v>
-      </c>
-      <c r="K14" t="s">
+      <c r="E14" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="G14" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="H14" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="I14" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="K14" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="O14" t="s">
+      <c r="O14" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="P14" t="s">
+      <c r="P14" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="R14" t="s">
+      <c r="R14" s="1" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="15" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="5" t="s">
+    <row r="15" spans="1:18" ht="87" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="B15">
+      <c r="B15" s="1">
         <v>16</v>
       </c>
-      <c r="D15" t="s">
+      <c r="D15" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="E15" t="s">
-        <v>74</v>
-      </c>
-      <c r="G15" t="s">
-        <v>73</v>
-      </c>
-      <c r="H15" t="s">
-        <v>89</v>
-      </c>
-      <c r="I15" t="s">
-        <v>99</v>
-      </c>
-      <c r="K15" t="s">
+      <c r="E15" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="G15" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="H15" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="I15" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="K15" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="O15" t="s">
+      <c r="O15" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="P15" t="s">
+      <c r="P15" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="R15" t="s">
+      <c r="R15" s="1" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="16" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="5" t="s">
+    <row r="16" spans="1:18" ht="87" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="B16">
+      <c r="B16" s="1">
         <v>6</v>
       </c>
-      <c r="D16" t="s">
+      <c r="D16" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="E16" t="s">
+      <c r="E16" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="G16" t="s">
-        <v>73</v>
-      </c>
-      <c r="H16" t="s">
-        <v>89</v>
-      </c>
-      <c r="I16" t="s">
-        <v>99</v>
-      </c>
-      <c r="K16" t="s">
+      <c r="G16" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="H16" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="I16" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="K16" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="O16" t="s">
+      <c r="O16" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="P16" t="s">
+      <c r="P16" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="R16" t="s">
+      <c r="R16" s="1" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="17" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="5" t="s">
+    <row r="17" spans="1:18" ht="87" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="B17">
+      <c r="B17" s="1">
         <v>6</v>
       </c>
-      <c r="D17" t="s">
+      <c r="D17" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="E17" t="s">
-        <v>74</v>
-      </c>
-      <c r="G17" t="s">
-        <v>73</v>
-      </c>
-      <c r="H17" t="s">
-        <v>89</v>
-      </c>
-      <c r="I17" t="s">
-        <v>99</v>
-      </c>
-      <c r="K17" t="s">
+      <c r="E17" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="G17" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="H17" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="I17" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="K17" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="O17" t="s">
+      <c r="O17" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="P17" t="s">
+      <c r="P17" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="R17" t="s">
+      <c r="R17" s="1" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="18" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="5" t="s">
+    <row r="18" spans="1:18" ht="87" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="B18">
+      <c r="B18" s="1">
         <v>5</v>
       </c>
-      <c r="D18" t="s">
+      <c r="D18" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="E18" t="s">
-        <v>74</v>
-      </c>
-      <c r="G18" t="s">
-        <v>73</v>
-      </c>
-      <c r="H18" t="s">
-        <v>89</v>
-      </c>
-      <c r="I18" t="s">
-        <v>99</v>
-      </c>
-      <c r="K18" t="s">
+      <c r="E18" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="G18" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="H18" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="I18" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="K18" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="O18" t="s">
+      <c r="O18" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="P18" t="s">
+      <c r="P18" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="R18" t="s">
+      <c r="R18" s="1" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="19" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="5" t="s">
+    <row r="19" spans="1:18" ht="87" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="B19">
+      <c r="B19" s="1">
         <v>14</v>
       </c>
-      <c r="D19" t="s">
+      <c r="D19" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="E19" t="s">
-        <v>74</v>
-      </c>
-      <c r="G19" t="s">
-        <v>73</v>
-      </c>
-      <c r="H19" t="s">
-        <v>89</v>
-      </c>
-      <c r="I19" t="s">
-        <v>99</v>
-      </c>
-      <c r="K19" t="s">
+      <c r="E19" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="G19" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="H19" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="I19" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="K19" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="O19" t="s">
+      <c r="O19" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="P19" t="s">
+      <c r="P19" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="R19" t="s">
+      <c r="R19" s="1" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="20" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="5" t="s">
+    <row r="20" spans="1:18" ht="87" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="B20">
+      <c r="B20" s="1">
         <v>14</v>
       </c>
-      <c r="D20" t="s">
+      <c r="D20" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="E20" t="s">
-        <v>74</v>
-      </c>
-      <c r="G20" t="s">
-        <v>73</v>
-      </c>
-      <c r="H20" t="s">
-        <v>89</v>
-      </c>
-      <c r="I20" t="s">
-        <v>99</v>
-      </c>
-      <c r="K20" t="s">
+      <c r="E20" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="G20" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="H20" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="I20" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="K20" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="O20" t="s">
+      <c r="O20" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="P20" t="s">
+      <c r="P20" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="R20" t="s">
+      <c r="R20" s="1" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="21" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="5" t="s">
+    <row r="21" spans="1:18" ht="87" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="B21">
+      <c r="B21" s="1">
         <v>17</v>
       </c>
-      <c r="D21" t="s">
+      <c r="D21" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="E21" t="s">
-        <v>74</v>
-      </c>
-      <c r="G21" t="s">
-        <v>73</v>
-      </c>
-      <c r="H21" t="s">
-        <v>89</v>
-      </c>
-      <c r="I21" t="s">
-        <v>99</v>
-      </c>
-      <c r="K21" t="s">
+      <c r="E21" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="G21" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="H21" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="I21" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="K21" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="O21" t="s">
+      <c r="O21" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="P21" t="s">
+      <c r="P21" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="R21" t="s">
+      <c r="R21" s="1" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="22" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="5" t="s">
+    <row r="22" spans="1:18" ht="87" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="B22">
+      <c r="B22" s="1">
         <v>17</v>
       </c>
-      <c r="D22" t="s">
+      <c r="D22" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="E22" t="s">
-        <v>74</v>
-      </c>
-      <c r="G22" t="s">
-        <v>73</v>
-      </c>
-      <c r="H22" t="s">
-        <v>89</v>
-      </c>
-      <c r="I22" t="s">
-        <v>99</v>
-      </c>
-      <c r="K22" t="s">
+      <c r="E22" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="G22" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="H22" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="I22" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="K22" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="O22" t="s">
+      <c r="O22" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="P22" t="s">
+      <c r="P22" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="R22" t="s">
+      <c r="R22" s="1" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="23" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="5" t="s">
+    <row r="23" spans="1:18" ht="87" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A23" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="B23">
+      <c r="B23" s="1">
         <v>8</v>
       </c>
-      <c r="D23" t="s">
+      <c r="D23" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="E23" t="s">
-        <v>74</v>
-      </c>
-      <c r="G23" t="s">
-        <v>73</v>
-      </c>
-      <c r="H23" t="s">
-        <v>89</v>
-      </c>
-      <c r="I23" t="s">
-        <v>99</v>
-      </c>
-      <c r="K23" t="s">
+      <c r="E23" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="G23" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="H23" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="I23" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="K23" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="O23" t="s">
+      <c r="O23" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="P23" t="s">
+      <c r="P23" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="R23" t="s">
+      <c r="R23" s="1" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="24" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="5" t="s">
+    <row r="24" spans="1:18" ht="87" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A24" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="B24">
+      <c r="B24" s="1">
         <v>7</v>
       </c>
-      <c r="D24" t="s">
+      <c r="D24" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="E24" t="s">
-        <v>74</v>
-      </c>
-      <c r="G24" t="s">
-        <v>73</v>
-      </c>
-      <c r="H24" t="s">
-        <v>89</v>
-      </c>
-      <c r="I24" t="s">
-        <v>99</v>
-      </c>
-      <c r="K24" t="s">
+      <c r="E24" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="G24" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="H24" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="I24" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="K24" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="O24" t="s">
+      <c r="O24" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="P24" t="s">
+      <c r="P24" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="R24" t="s">
+      <c r="R24" s="1" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="25" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="5" t="s">
+    <row r="25" spans="1:18" ht="87" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="B25">
+      <c r="B25" s="1">
         <v>7</v>
       </c>
-      <c r="D25" t="s">
+      <c r="D25" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="E25" t="s">
-        <v>74</v>
-      </c>
-      <c r="G25" t="s">
-        <v>73</v>
-      </c>
-      <c r="H25" t="s">
-        <v>89</v>
-      </c>
-      <c r="I25" t="s">
-        <v>99</v>
-      </c>
-      <c r="K25" t="s">
+      <c r="E25" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="G25" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="H25" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="I25" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="K25" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="O25" t="s">
+      <c r="O25" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="P25" t="s">
+      <c r="P25" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="R25" t="s">
+      <c r="R25" s="1" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="26" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="5" t="s">
+    <row r="26" spans="1:18" ht="87" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="B26">
+      <c r="B26" s="1">
         <v>12</v>
       </c>
-      <c r="D26" t="s">
+      <c r="D26" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="E26" t="s">
-        <v>74</v>
-      </c>
-      <c r="G26" t="s">
-        <v>73</v>
-      </c>
-      <c r="H26" t="s">
-        <v>89</v>
-      </c>
-      <c r="I26" t="s">
-        <v>99</v>
-      </c>
-      <c r="K26" t="s">
+      <c r="E26" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="G26" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="H26" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="I26" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="K26" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="O26" t="s">
+      <c r="O26" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="P26" t="s">
+      <c r="P26" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="R26" t="s">
+      <c r="R26" s="1" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="27" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="5" t="s">
+    <row r="27" spans="1:18" ht="87" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A27" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="B27">
+      <c r="B27" s="1">
         <v>12</v>
       </c>
-      <c r="D27" t="s">
+      <c r="D27" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="E27" t="s">
-        <v>74</v>
-      </c>
-      <c r="G27" t="s">
-        <v>73</v>
-      </c>
-      <c r="H27" t="s">
-        <v>89</v>
-      </c>
-      <c r="I27" t="s">
-        <v>99</v>
-      </c>
-      <c r="K27" t="s">
+      <c r="E27" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="G27" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="H27" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="I27" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="K27" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="O27" t="s">
+      <c r="O27" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="P27" t="s">
+      <c r="P27" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="R27" t="s">
+      <c r="R27" s="1" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="28" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="5" t="s">
+    <row r="28" spans="1:18" ht="87" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A28" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="B28">
+      <c r="B28" s="1">
         <v>9</v>
       </c>
-      <c r="D28" t="s">
+      <c r="D28" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="E28" t="s">
-        <v>74</v>
-      </c>
-      <c r="G28" t="s">
-        <v>73</v>
-      </c>
-      <c r="H28" t="s">
-        <v>89</v>
-      </c>
-      <c r="I28" t="s">
-        <v>99</v>
-      </c>
-      <c r="K28" t="s">
+      <c r="E28" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="G28" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="H28" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="I28" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="K28" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="O28" t="s">
+      <c r="O28" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="P28" t="s">
+      <c r="P28" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="R28" t="s">
+      <c r="R28" s="1" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="29" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="5" t="s">
+    <row r="29" spans="1:18" ht="87" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A29" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="B29">
+      <c r="B29" s="1">
         <v>18</v>
       </c>
-      <c r="D29" t="s">
+      <c r="D29" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="E29" t="s">
-        <v>74</v>
-      </c>
-      <c r="G29" t="s">
-        <v>73</v>
-      </c>
-      <c r="H29" t="s">
-        <v>89</v>
-      </c>
-      <c r="I29" t="s">
-        <v>99</v>
-      </c>
-      <c r="K29" t="s">
+      <c r="E29" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="G29" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="H29" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="I29" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="K29" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="O29" t="s">
+      <c r="O29" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="P29" t="s">
+      <c r="P29" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="R29" t="s">
+      <c r="R29" s="1" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="30" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="5" t="s">
+    <row r="30" spans="1:18" ht="87" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A30" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="B30">
+      <c r="B30" s="1">
         <v>11</v>
       </c>
-      <c r="D30" t="s">
+      <c r="D30" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="E30" t="s">
-        <v>74</v>
-      </c>
-      <c r="G30" t="s">
-        <v>73</v>
-      </c>
-      <c r="H30" t="s">
-        <v>89</v>
-      </c>
-      <c r="I30" t="s">
-        <v>99</v>
-      </c>
-      <c r="K30" t="s">
+      <c r="E30" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="G30" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="H30" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="I30" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="K30" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="O30" t="s">
+      <c r="O30" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="P30" t="s">
+      <c r="P30" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="R30" t="s">
+      <c r="R30" s="1" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="31" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="5" t="s">
+    <row r="31" spans="1:18" ht="87" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A31" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="B31">
+      <c r="B31" s="1">
         <v>11</v>
       </c>
-      <c r="D31" t="s">
+      <c r="D31" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="E31" t="s">
-        <v>74</v>
-      </c>
-      <c r="G31" t="s">
-        <v>73</v>
-      </c>
-      <c r="H31" t="s">
-        <v>89</v>
-      </c>
-      <c r="I31" t="s">
-        <v>99</v>
-      </c>
-      <c r="K31" t="s">
+      <c r="E31" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="G31" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="H31" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="I31" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="K31" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="O31" t="s">
+      <c r="O31" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="P31" t="s">
+      <c r="P31" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="R31" t="s">
+      <c r="R31" s="1" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="32" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="5" t="s">
+    <row r="32" spans="1:18" ht="87" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A32" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="B32">
+      <c r="B32" s="1">
         <v>10</v>
       </c>
-      <c r="D32" t="s">
+      <c r="D32" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="E32" t="s">
-        <v>74</v>
-      </c>
-      <c r="G32" t="s">
-        <v>73</v>
-      </c>
-      <c r="H32" t="s">
-        <v>89</v>
-      </c>
-      <c r="I32" t="s">
-        <v>99</v>
-      </c>
-      <c r="K32" t="s">
+      <c r="E32" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="G32" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="H32" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="I32" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="K32" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="O32" t="s">
+      <c r="O32" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="P32" t="s">
+      <c r="P32" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="R32" t="s">
+      <c r="R32" s="1" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="33" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="8" t="s">
+    <row r="33" spans="1:18" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A33" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="D33" t="s">
+      <c r="D33" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="E33" t="s">
-        <v>74</v>
-      </c>
-      <c r="G33" t="s">
-        <v>73</v>
-      </c>
-      <c r="H33" t="s">
+      <c r="E33" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="G33" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="H33" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="I33" t="s">
-        <v>99</v>
-      </c>
-      <c r="Q33" t="s">
+      <c r="I33" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="Q33" s="1" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="34" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A34" s="8" t="s">
+    <row r="34" spans="1:18" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A34" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="D34" t="s">
+      <c r="D34" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="E34" t="s">
-        <v>74</v>
-      </c>
-      <c r="G34" t="s">
-        <v>73</v>
-      </c>
-      <c r="H34" t="s">
+      <c r="E34" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="G34" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="H34" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="I34" t="s">
-        <v>99</v>
-      </c>
-      <c r="Q34" t="s">
+      <c r="I34" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="Q34" s="1" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="35" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A35" s="8" t="s">
+    <row r="35" spans="1:18" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A35" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="D35" t="s">
+      <c r="D35" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="E35" t="s">
-        <v>74</v>
-      </c>
-      <c r="G35" t="s">
-        <v>73</v>
-      </c>
-      <c r="H35" t="s">
+      <c r="E35" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="G35" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="H35" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="I35" t="s">
-        <v>99</v>
-      </c>
-      <c r="Q35" t="s">
+      <c r="I35" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="Q35" s="1" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="36" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="8" t="s">
+    <row r="36" spans="1:18" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A36" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="D36" t="s">
+      <c r="D36" s="1" t="s">
         <v>170</v>
       </c>
-      <c r="E36" t="s">
-        <v>74</v>
-      </c>
-      <c r="G36" t="s">
-        <v>73</v>
-      </c>
-      <c r="H36" t="s">
+      <c r="E36" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="G36" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="H36" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="I36" t="s">
-        <v>99</v>
-      </c>
-      <c r="Q36" t="s">
+      <c r="I36" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="Q36" s="1" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="37" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A37" s="8" t="s">
+    <row r="37" spans="1:18" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A37" s="5" t="s">
         <v>96</v>
       </c>
-      <c r="D37" t="s">
+      <c r="D37" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="E37" t="s">
-        <v>74</v>
-      </c>
-      <c r="G37" t="s">
-        <v>73</v>
-      </c>
-      <c r="H37" t="s">
+      <c r="E37" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="G37" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="H37" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="I37" t="s">
-        <v>99</v>
-      </c>
-      <c r="Q37" t="s">
+      <c r="I37" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="Q37" s="1" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="38" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A38" s="8" t="s">
+    <row r="38" spans="1:18" ht="29" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A38" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="D38" t="s">
+      <c r="D38" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="E38" t="s">
-        <v>74</v>
-      </c>
-      <c r="G38" t="s">
-        <v>73</v>
-      </c>
-      <c r="H38" t="s">
+      <c r="E38" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="G38" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="H38" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="J38" t="s">
+      <c r="J38" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="L38" t="s">
+      <c r="L38" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="M38" t="s">
+      <c r="M38" s="1" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="39" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A39" s="8" t="s">
+    <row r="39" spans="1:18" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A39" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="D39" t="s">
+      <c r="D39" s="1" t="s">
         <v>173</v>
       </c>
-      <c r="E39" t="s">
-        <v>74</v>
-      </c>
-      <c r="G39" t="s">
-        <v>73</v>
-      </c>
-      <c r="H39" t="s">
-        <v>89</v>
-      </c>
-      <c r="I39" t="s">
-        <v>99</v>
-      </c>
-      <c r="Q39" t="s">
+      <c r="E39" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="G39" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="H39" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="I39" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="Q39" s="1" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="40" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A40" s="8" t="s">
+    <row r="40" spans="1:18" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A40" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="D40" t="s">
+      <c r="D40" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="E40" t="s">
-        <v>74</v>
-      </c>
-      <c r="G40" t="s">
-        <v>73</v>
-      </c>
-      <c r="H40" t="s">
-        <v>89</v>
-      </c>
-      <c r="I40" t="s">
-        <v>99</v>
-      </c>
-      <c r="K40" t="s">
+      <c r="E40" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="G40" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="H40" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="I40" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="K40" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="O40" t="s">
+      <c r="O40" s="1" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="41" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A41" s="8" t="s">
+    <row r="41" spans="1:18" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A41" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="D41" t="s">
+      <c r="D41" s="1" t="s">
         <v>175</v>
       </c>
-      <c r="E41" t="s">
-        <v>74</v>
-      </c>
-      <c r="G41" t="s">
-        <v>73</v>
-      </c>
-      <c r="H41" t="s">
-        <v>89</v>
-      </c>
-      <c r="I41" t="s">
-        <v>99</v>
-      </c>
-      <c r="K41" t="s">
+      <c r="E41" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="G41" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="H41" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="I41" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="K41" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="O41" t="s">
+      <c r="O41" s="1" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="42" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A42" s="8" t="s">
+    <row r="42" spans="1:18" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A42" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="D42" t="s">
+      <c r="D42" s="1" t="s">
         <v>176</v>
       </c>
-      <c r="E42" t="s">
-        <v>74</v>
-      </c>
-      <c r="G42" t="s">
-        <v>73</v>
-      </c>
-      <c r="H42" t="s">
-        <v>89</v>
-      </c>
-      <c r="I42" t="s">
-        <v>99</v>
-      </c>
-      <c r="K42" t="s">
+      <c r="E42" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="G42" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="H42" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="I42" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="K42" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="O42" t="s">
+      <c r="O42" s="1" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="43" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A43" s="3" t="s">
+    <row r="43" spans="1:18" ht="29" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A43" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="D43" t="s">
+      <c r="D43" s="1" t="s">
         <v>177</v>
       </c>
-      <c r="E43" t="s">
-        <v>74</v>
-      </c>
-      <c r="G43" t="s">
-        <v>73</v>
-      </c>
-      <c r="H43" t="s">
+      <c r="E43" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="G43" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="H43" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="J43" t="s">
+      <c r="J43" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="L43" t="s">
+      <c r="L43" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="M43" t="s">
+      <c r="M43" s="1" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="44" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A44" s="4" t="s">
+    <row r="44" spans="1:18" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A44" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="D44" t="s">
+      <c r="D44" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="E44" t="s">
-        <v>74</v>
-      </c>
-      <c r="G44" t="s">
-        <v>73</v>
-      </c>
-      <c r="H44" t="s">
-        <v>89</v>
-      </c>
-      <c r="I44" t="s">
-        <v>99</v>
-      </c>
-      <c r="Q44" t="s">
+      <c r="E44" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="G44" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="H44" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="I44" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="Q44" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="R44" t="s">
+      <c r="R44" s="1" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="45" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A45" s="4" t="s">
+    <row r="45" spans="1:18" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A45" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="D45" t="s">
+      <c r="D45" s="1" t="s">
         <v>179</v>
       </c>
-      <c r="E45" t="s">
-        <v>74</v>
-      </c>
-      <c r="G45" t="s">
-        <v>73</v>
-      </c>
-      <c r="H45" t="s">
-        <v>89</v>
-      </c>
-      <c r="I45" t="s">
-        <v>99</v>
-      </c>
-      <c r="Q45" t="s">
+      <c r="E45" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="G45" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="H45" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="I45" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="Q45" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="R45" t="s">
+      <c r="R45" s="1" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="46" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A46" s="4" t="s">
+    <row r="46" spans="1:18" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A46" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="D46" t="s">
+      <c r="D46" s="1" t="s">
         <v>180</v>
       </c>
-      <c r="E46" t="s">
-        <v>74</v>
-      </c>
-      <c r="G46" t="s">
-        <v>73</v>
-      </c>
-      <c r="H46" t="s">
-        <v>89</v>
-      </c>
-      <c r="I46" t="s">
-        <v>99</v>
-      </c>
-      <c r="Q46" t="s">
+      <c r="E46" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="G46" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="H46" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="I46" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="Q46" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="R46" t="s">
+      <c r="R46" s="1" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="47" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A47" s="4" t="s">
+    <row r="47" spans="1:18" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A47" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="D47" t="s">
+      <c r="D47" s="1" t="s">
         <v>181</v>
       </c>
-      <c r="E47" t="s">
-        <v>74</v>
-      </c>
-      <c r="G47" t="s">
-        <v>73</v>
-      </c>
-      <c r="H47" t="s">
-        <v>89</v>
-      </c>
-      <c r="I47" t="s">
-        <v>99</v>
-      </c>
-      <c r="Q47" t="s">
+      <c r="E47" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="G47" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="H47" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="I47" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="Q47" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="R47" t="s">
+      <c r="R47" s="1" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="48" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A48" s="4" t="s">
+    <row r="48" spans="1:18" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A48" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="D48" t="s">
+      <c r="D48" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="E48" t="s">
-        <v>74</v>
-      </c>
-      <c r="G48" t="s">
-        <v>73</v>
-      </c>
-      <c r="H48" t="s">
-        <v>89</v>
-      </c>
-      <c r="I48" t="s">
-        <v>99</v>
-      </c>
-      <c r="Q48" t="s">
+      <c r="E48" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="G48" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="H48" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="I48" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="Q48" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="R48" t="s">
+      <c r="R48" s="1" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="49" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A49" s="4" t="s">
+    <row r="49" spans="1:18" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A49" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="D49" t="s">
+      <c r="D49" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="E49" t="s">
-        <v>74</v>
-      </c>
-      <c r="G49" t="s">
-        <v>73</v>
-      </c>
-      <c r="H49" t="s">
-        <v>89</v>
-      </c>
-      <c r="I49" t="s">
-        <v>99</v>
-      </c>
-      <c r="Q49" t="s">
+      <c r="E49" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="G49" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="H49" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="I49" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="Q49" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="R49" t="s">
+      <c r="R49" s="1" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="50" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A50" s="2" t="s">
+    <row r="50" spans="1:18" ht="101.5" x14ac:dyDescent="0.35">
+      <c r="A50" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="D50" t="s">
+      <c r="D50" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="E50" t="s">
-        <v>74</v>
-      </c>
-      <c r="G50" t="s">
-        <v>73</v>
-      </c>
-      <c r="H50" t="s">
+      <c r="E50" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="G50" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="H50" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="J50" t="s">
+      <c r="J50" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="L50" t="s">
+      <c r="L50" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="M50" t="s">
+      <c r="M50" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="N50" t="s">
+      <c r="N50" s="1" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="51" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A51" s="2" t="s">
+    <row r="51" spans="1:18" ht="101.5" x14ac:dyDescent="0.35">
+      <c r="A51" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="D51" t="s">
+      <c r="D51" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="E51" t="s">
-        <v>74</v>
-      </c>
-      <c r="G51" t="s">
-        <v>73</v>
-      </c>
-      <c r="H51" t="s">
+      <c r="E51" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="G51" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="H51" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="J51" t="s">
+      <c r="J51" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="L51" t="s">
+      <c r="L51" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="M51" t="s">
+      <c r="M51" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="N51" t="s">
+      <c r="N51" s="1" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="52" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A52" s="2" t="s">
+    <row r="52" spans="1:18" ht="101.5" x14ac:dyDescent="0.35">
+      <c r="A52" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="D52" t="s">
+      <c r="D52" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="E52" t="s">
-        <v>74</v>
-      </c>
-      <c r="G52" t="s">
-        <v>73</v>
-      </c>
-      <c r="H52" t="s">
+      <c r="E52" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="G52" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="H52" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="J52" t="s">
+      <c r="J52" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="L52" t="s">
+      <c r="L52" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="M52" t="s">
+      <c r="M52" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="N52" t="s">
+      <c r="N52" s="1" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="53" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A53" s="2" t="s">
+    <row r="53" spans="1:18" ht="101.5" x14ac:dyDescent="0.35">
+      <c r="A53" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="D53" t="s">
+      <c r="D53" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="E53" t="s">
-        <v>74</v>
-      </c>
-      <c r="G53" t="s">
-        <v>73</v>
-      </c>
-      <c r="H53" t="s">
+      <c r="E53" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="G53" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="H53" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="J53" t="s">
+      <c r="J53" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="L53" t="s">
+      <c r="L53" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="M53" t="s">
+      <c r="M53" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="N53" t="s">
+      <c r="N53" s="1" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="54" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A54" s="2" t="s">
+    <row r="54" spans="1:18" ht="101.5" x14ac:dyDescent="0.35">
+      <c r="A54" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="D54" t="s">
+      <c r="D54" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="E54" t="s">
-        <v>74</v>
-      </c>
-      <c r="G54" t="s">
-        <v>73</v>
-      </c>
-      <c r="H54" t="s">
+      <c r="E54" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="G54" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="H54" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="J54" t="s">
+      <c r="J54" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="L54" t="s">
+      <c r="L54" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="M54" t="s">
+      <c r="M54" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="N54" t="s">
+      <c r="N54" s="1" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="55" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A55" s="6" t="s">
+    <row r="55" spans="1:18" ht="101.5" x14ac:dyDescent="0.35">
+      <c r="A55" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="D55" t="s">
+      <c r="D55" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="E55" t="s">
-        <v>74</v>
-      </c>
-      <c r="G55" t="s">
-        <v>73</v>
-      </c>
-      <c r="H55" t="s">
+      <c r="E55" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="G55" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="H55" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="I55" t="s">
+      <c r="I55" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="Q55" t="s">
+      <c r="Q55" s="1" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="56" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A56" s="6" t="s">
+    <row r="56" spans="1:18" ht="101.5" x14ac:dyDescent="0.35">
+      <c r="A56" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="D56" t="s">
+      <c r="D56" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="E56" t="s">
-        <v>74</v>
-      </c>
-      <c r="G56" t="s">
-        <v>73</v>
-      </c>
-      <c r="H56" t="s">
+      <c r="E56" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="G56" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="H56" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="I56" t="s">
+      <c r="I56" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="Q56" t="s">
+      <c r="Q56" s="1" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="57" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A57" s="6" t="s">
+    <row r="57" spans="1:18" ht="101.5" x14ac:dyDescent="0.35">
+      <c r="A57" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="D57" t="s">
+      <c r="D57" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="E57" t="s">
-        <v>74</v>
-      </c>
-      <c r="G57" t="s">
-        <v>73</v>
-      </c>
-      <c r="H57" t="s">
+      <c r="E57" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="G57" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="H57" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="I57" t="s">
+      <c r="I57" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="Q57" t="s">
+      <c r="Q57" s="1" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="58" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A58" s="6" t="s">
+    <row r="58" spans="1:18" ht="101.5" x14ac:dyDescent="0.35">
+      <c r="A58" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="D58" t="s">
+      <c r="D58" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="E58" t="s">
-        <v>74</v>
-      </c>
-      <c r="G58" t="s">
-        <v>73</v>
-      </c>
-      <c r="H58" t="s">
+      <c r="E58" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="G58" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="H58" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="I58" t="s">
+      <c r="I58" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="Q58" t="s">
+      <c r="Q58" s="1" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="59" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A59" s="6" t="s">
+    <row r="59" spans="1:18" ht="101.5" x14ac:dyDescent="0.35">
+      <c r="A59" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="D59" t="s">
+      <c r="D59" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="E59" t="s">
-        <v>74</v>
-      </c>
-      <c r="G59" t="s">
-        <v>73</v>
-      </c>
-      <c r="H59" t="s">
+      <c r="E59" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="G59" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="H59" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="I59" t="s">
-        <v>99</v>
-      </c>
-      <c r="Q59" t="s">
+      <c r="I59" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="Q59" s="1" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="60" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A60" s="6" t="s">
+    <row r="60" spans="1:18" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="A60" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="D60" t="s">
+      <c r="D60" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="E60" t="s">
-        <v>74</v>
-      </c>
-      <c r="G60" t="s">
-        <v>73</v>
-      </c>
-      <c r="H60" t="s">
+      <c r="E60" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="G60" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="H60" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="I60" t="s">
+      <c r="I60" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="Q60" t="s">
+      <c r="Q60" s="1" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="61" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A61" s="6" t="s">
+    <row r="61" spans="1:18" ht="188.5" x14ac:dyDescent="0.35">
+      <c r="A61" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="D61" t="s">
+      <c r="D61" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="E61" t="s">
-        <v>74</v>
-      </c>
-      <c r="G61" t="s">
-        <v>73</v>
-      </c>
-      <c r="H61" t="s">
+      <c r="E61" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="G61" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="H61" s="1" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="62" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A62" s="6" t="s">
+    <row r="62" spans="1:18" ht="188.5" x14ac:dyDescent="0.35">
+      <c r="A62" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="D62" t="s">
+      <c r="D62" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="E62" t="s">
-        <v>74</v>
-      </c>
-      <c r="G62" t="s">
-        <v>73</v>
-      </c>
-      <c r="H62" t="s">
+      <c r="E62" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="G62" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="H62" s="1" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="63" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A63" s="6" t="s">
+    <row r="63" spans="1:18" ht="188.5" x14ac:dyDescent="0.35">
+      <c r="A63" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="D63" t="s">
+      <c r="D63" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="E63" t="s">
-        <v>74</v>
-      </c>
-      <c r="G63" t="s">
-        <v>73</v>
-      </c>
-      <c r="H63" t="s">
+      <c r="E63" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="G63" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="H63" s="1" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="64" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A64" s="6" t="s">
+    <row r="64" spans="1:18" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="A64" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="D64" t="s">
+      <c r="D64" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="E64" t="s">
-        <v>74</v>
-      </c>
-      <c r="G64" t="s">
-        <v>73</v>
-      </c>
-      <c r="H64" t="s">
+      <c r="E64" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="G64" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="H64" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="I64" t="s">
-        <v>99</v>
-      </c>
-      <c r="Q64" t="s">
+      <c r="I64" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="Q64" s="1" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="65" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A65" s="6" t="s">
+    <row r="65" spans="1:18" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="A65" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="D65" t="s">
+      <c r="D65" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="E65" t="s">
-        <v>74</v>
-      </c>
-      <c r="G65" t="s">
-        <v>73</v>
-      </c>
-      <c r="H65" t="s">
+      <c r="E65" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="G65" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="H65" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="I65" t="s">
+      <c r="I65" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="Q65" t="s">
+      <c r="Q65" s="1" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="66" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A66" s="6" t="s">
+    <row r="66" spans="1:18" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="A66" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="D66" t="s">
+      <c r="D66" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="E66" t="s">
-        <v>74</v>
-      </c>
-      <c r="G66" t="s">
-        <v>73</v>
-      </c>
-      <c r="H66" t="s">
+      <c r="E66" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="G66" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="H66" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="I66" t="s">
-        <v>99</v>
-      </c>
-      <c r="Q66" t="s">
+      <c r="I66" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="Q66" s="1" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="67" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A67" s="6" t="s">
+    <row r="67" spans="1:18" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="A67" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="D67" t="s">
+      <c r="D67" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="E67" t="s">
-        <v>74</v>
-      </c>
-      <c r="G67" t="s">
-        <v>73</v>
-      </c>
-      <c r="H67" t="s">
+      <c r="E67" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="G67" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="H67" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="I67" t="s">
-        <v>99</v>
-      </c>
-      <c r="Q67" t="s">
+      <c r="I67" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="Q67" s="1" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="68" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A68" s="6" t="s">
+    <row r="68" spans="1:18" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="A68" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="D68" t="s">
+      <c r="D68" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="E68" t="s">
-        <v>74</v>
-      </c>
-      <c r="G68" t="s">
-        <v>73</v>
-      </c>
-      <c r="H68" t="s">
+      <c r="E68" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="G68" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="H68" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="I68" t="s">
-        <v>99</v>
-      </c>
-      <c r="Q68" t="s">
+      <c r="I68" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="Q68" s="1" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="69" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A69" s="6" t="s">
+    <row r="69" spans="1:18" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="A69" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="D69" t="s">
+      <c r="D69" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="E69" t="s">
-        <v>74</v>
-      </c>
-      <c r="G69" t="s">
-        <v>73</v>
-      </c>
-      <c r="H69" t="s">
+      <c r="E69" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="G69" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="H69" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="I69" t="s">
-        <v>99</v>
-      </c>
-      <c r="Q69" t="s">
+      <c r="I69" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="Q69" s="1" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="70" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A70" s="6" t="s">
+    <row r="70" spans="1:18" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="A70" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="D70" t="s">
+      <c r="D70" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="E70" t="s">
-        <v>74</v>
-      </c>
-      <c r="G70" t="s">
-        <v>73</v>
-      </c>
-      <c r="H70" t="s">
+      <c r="E70" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="G70" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="H70" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="I70" t="s">
+      <c r="I70" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="Q70" t="s">
+      <c r="Q70" s="1" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="71" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A71" s="7" t="s">
+    <row r="71" spans="1:18" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="A71" s="9" t="s">
         <v>71</v>
       </c>
-      <c r="D71" t="s">
+      <c r="D71" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="E71" t="s">
-        <v>74</v>
-      </c>
-      <c r="G71" t="s">
-        <v>73</v>
-      </c>
-      <c r="H71" t="s">
+      <c r="E71" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="G71" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="H71" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="I71" t="s">
+      <c r="I71" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="Q71" t="s">
+      <c r="Q71" s="1" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="72" spans="1:18" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A72" s="7" t="s">
+    <row r="72" spans="1:18" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="A72" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="D72" t="s">
+      <c r="D72" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="E72" t="s">
-        <v>74</v>
-      </c>
-      <c r="G72" t="s">
-        <v>73</v>
-      </c>
-      <c r="H72" t="s">
+      <c r="E72" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="G72" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="H72" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="I72" t="s">
+      <c r="I72" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="Q72" t="s">
+      <c r="Q72" s="1" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="73" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A73" s="10" t="s">
+    <row r="73" spans="1:18" ht="130.5" x14ac:dyDescent="0.35">
+      <c r="A73" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C73" t="s">
+      <c r="C73" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="D73" t="s">
+      <c r="D73" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="E73" t="s">
+      <c r="E73" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="G73" t="s">
-        <v>73</v>
-      </c>
-      <c r="H73" t="s">
+      <c r="G73" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="H73" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="I73" t="s">
-        <v>99</v>
-      </c>
-      <c r="K73" t="s">
+      <c r="I73" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="K73" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="Q73" t="s">
+      <c r="Q73" s="1" t="s">
         <v>186</v>
       </c>
     </row>
-    <row r="74" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A74" s="11" t="s">
+    <row r="74" spans="1:18" ht="58" x14ac:dyDescent="0.35">
+      <c r="A74" s="10" t="s">
         <v>75</v>
       </c>
-      <c r="C74" t="s">
+      <c r="C74" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="D74" t="s">
+      <c r="D74" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="E74" t="s">
+      <c r="E74" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="F74" t="s">
+      <c r="F74" s="1" t="s">
         <v>185</v>
       </c>
-      <c r="G74" t="s">
-        <v>73</v>
-      </c>
-      <c r="H74" t="s">
+      <c r="G74" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="H74" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="J74" t="s">
+      <c r="J74" s="1" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="75" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A75" s="11" t="s">
+    <row r="75" spans="1:18" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="A75" s="10" t="s">
         <v>76</v>
       </c>
-      <c r="C75" t="s">
+      <c r="C75" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="D75" t="s">
+      <c r="D75" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="E75" t="s">
+      <c r="E75" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="G75" t="s">
-        <v>73</v>
-      </c>
-      <c r="H75" t="s">
+      <c r="G75" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="H75" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="I75" t="s">
-        <v>99</v>
-      </c>
-      <c r="Q75" t="s">
+      <c r="I75" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="Q75" s="1" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="76" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A76" s="11" t="s">
+    <row r="76" spans="1:18" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="A76" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="C76" t="s">
+      <c r="C76" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="E76" t="s">
+      <c r="E76" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="G76" t="s">
-        <v>73</v>
-      </c>
-      <c r="H76" t="s">
+      <c r="G76" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="H76" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="I76" t="s">
-        <v>99</v>
-      </c>
-      <c r="Q76" t="s">
+      <c r="I76" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="Q76" s="1" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="77" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A77" s="9" t="s">
+    <row r="77" spans="1:18" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="A77" s="11" t="s">
         <v>78</v>
       </c>
-      <c r="D77" t="s">
+      <c r="D77" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="E77" t="s">
+      <c r="E77" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="G77" t="s">
-        <v>73</v>
-      </c>
-      <c r="H77" t="s">
+      <c r="G77" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="H77" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="I77" t="s">
-        <v>99</v>
-      </c>
-      <c r="Q77" t="s">
+      <c r="I77" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="Q77" s="1" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="78" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A78" s="9" t="s">
+    <row r="78" spans="1:18" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="A78" s="11" t="s">
         <v>79</v>
       </c>
-      <c r="D78" t="s">
+      <c r="D78" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="E78" t="s">
+      <c r="E78" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="G78" t="s">
-        <v>73</v>
-      </c>
-      <c r="H78" t="s">
+      <c r="G78" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="H78" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="I78" t="s">
-        <v>99</v>
-      </c>
-      <c r="Q78" t="s">
+      <c r="I78" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="Q78" s="1" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="79" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A79" s="11" t="s">
+    <row r="79" spans="1:18" ht="58" x14ac:dyDescent="0.35">
+      <c r="A79" s="10" t="s">
         <v>127</v>
       </c>
-      <c r="F79" t="s">
+      <c r="F79" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="G79" t="s">
-        <v>73</v>
-      </c>
-      <c r="H79" t="s">
+      <c r="G79" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="H79" s="1" t="s">
         <v>191</v>
       </c>
-      <c r="Q79" t="s">
+      <c r="Q79" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="R79" t="s">
+      <c r="R79" s="1" t="s">
         <v>200</v>
       </c>
     </row>
-    <row r="80" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A80" s="11" t="s">
+    <row r="80" spans="1:18" ht="130.5" x14ac:dyDescent="0.35">
+      <c r="A80" s="10" t="s">
         <v>128</v>
       </c>
-      <c r="C80" t="s">
+      <c r="C80" s="1" t="s">
         <v>188</v>
       </c>
-      <c r="E80" t="s">
+      <c r="E80" s="1" t="s">
         <v>189</v>
       </c>
-      <c r="F80" t="s">
+      <c r="F80" s="1" t="s">
         <v>190</v>
       </c>
-      <c r="G80" t="s">
-        <v>73</v>
-      </c>
-      <c r="H80" t="s">
+      <c r="G80" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="H80" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="I80" t="s">
-        <v>99</v>
-      </c>
-      <c r="J80" t="s">
+      <c r="I80" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="J80" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="K80" t="s">
+      <c r="K80" s="1" t="s">
         <v>193</v>
       </c>
-      <c r="L80" t="s">
+      <c r="L80" s="1" t="s">
         <v>194</v>
       </c>
-      <c r="M80" t="s">
+      <c r="M80" s="1" t="s">
         <v>195</v>
       </c>
-      <c r="O80" t="s">
+      <c r="O80" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="P80" t="s">
+      <c r="P80" s="1" t="s">
         <v>197</v>
       </c>
-      <c r="Q80" t="s">
+      <c r="Q80" s="1" t="s">
         <v>198</v>
       </c>
-      <c r="R80" t="s">
+      <c r="R80" s="1" t="s">
         <v>199</v>
       </c>
     </row>
-    <row r="81" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:16" ht="58" x14ac:dyDescent="0.35">
       <c r="A81" s="12" t="s">
         <v>202</v>
       </c>
-      <c r="E81" t="s">
+      <c r="E81" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="G81" t="s">
+      <c r="G81" s="1" t="s">
         <v>222</v>
       </c>
-      <c r="H81" t="s">
+      <c r="H81" s="1" t="s">
         <v>217</v>
       </c>
-      <c r="J81" t="s">
+      <c r="J81" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="O81" t="s">
+      <c r="O81" s="1" t="s">
         <v>225</v>
       </c>
-      <c r="P81" t="s">
+      <c r="P81" s="1" t="s">
         <v>216</v>
       </c>
     </row>
-    <row r="82" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:16" ht="58" x14ac:dyDescent="0.35">
       <c r="A82" s="12" t="s">
         <v>203</v>
       </c>
-      <c r="E82" t="s">
+      <c r="E82" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="G82" t="s">
+      <c r="G82" s="1" t="s">
         <v>222</v>
       </c>
-      <c r="H82" t="s">
+      <c r="H82" s="1" t="s">
         <v>217</v>
       </c>
-      <c r="J82" t="s">
+      <c r="J82" s="1" t="s">
         <v>212</v>
       </c>
-      <c r="O82" t="s">
+      <c r="O82" s="1" t="s">
         <v>225</v>
       </c>
-      <c r="P82" t="s">
+      <c r="P82" s="1" t="s">
         <v>216</v>
       </c>
     </row>
-    <row r="83" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:16" ht="58" x14ac:dyDescent="0.35">
       <c r="A83" s="12" t="s">
         <v>204</v>
       </c>
-      <c r="E83" t="s">
+      <c r="E83" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="G83" t="s">
+      <c r="G83" s="1" t="s">
         <v>222</v>
       </c>
-      <c r="H83" t="s">
+      <c r="H83" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="J83" t="s">
+      <c r="J83" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="M83" t="s">
+      <c r="M83" s="1" t="s">
         <v>213</v>
       </c>
-      <c r="N83" t="s">
+      <c r="N83" s="1" t="s">
         <v>215</v>
       </c>
-      <c r="P83" t="s">
+      <c r="P83" s="1" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="84" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:16" ht="58" x14ac:dyDescent="0.35">
       <c r="A84" s="12" t="s">
         <v>205</v>
       </c>
-      <c r="E84" t="s">
+      <c r="E84" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="G84" t="s">
+      <c r="G84" s="1" t="s">
         <v>222</v>
       </c>
-      <c r="H84" t="s">
+      <c r="H84" s="1" t="s">
         <v>218</v>
       </c>
-      <c r="J84" t="s">
+      <c r="J84" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="M84" t="s">
+      <c r="M84" s="1" t="s">
         <v>223</v>
       </c>
-      <c r="N84" t="s">
+      <c r="N84" s="1" t="s">
         <v>215</v>
       </c>
-      <c r="P84" t="s">
+      <c r="P84" s="1" t="s">
         <v>216</v>
       </c>
     </row>
-    <row r="85" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:16" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A85" s="12" t="s">
         <v>206</v>
       </c>
-      <c r="E85" t="s">
+      <c r="E85" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="G85" t="s">
+      <c r="G85" s="1" t="s">
         <v>222</v>
       </c>
-      <c r="H85" t="s">
+      <c r="H85" s="1" t="s">
         <v>219</v>
       </c>
-      <c r="J85" t="s">
+      <c r="J85" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="O85" t="s">
+      <c r="O85" s="1" t="s">
         <v>225</v>
       </c>
-      <c r="P85" t="s">
+      <c r="P85" s="1" t="s">
         <v>216</v>
       </c>
     </row>
-    <row r="86" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:16" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A86" s="12" t="s">
         <v>207</v>
       </c>
-      <c r="E86" t="s">
+      <c r="E86" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="G86" t="s">
+      <c r="G86" s="1" t="s">
         <v>222</v>
       </c>
-      <c r="H86" t="s">
+      <c r="H86" s="1" t="s">
         <v>219</v>
       </c>
-      <c r="J86" t="s">
+      <c r="J86" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="O86" t="s">
+      <c r="O86" s="1" t="s">
         <v>225</v>
       </c>
-      <c r="P86" t="s">
+      <c r="P86" s="1" t="s">
         <v>216</v>
       </c>
     </row>
-    <row r="87" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:16" ht="58" x14ac:dyDescent="0.35">
       <c r="A87" s="12" t="s">
         <v>208</v>
       </c>
-      <c r="E87" t="s">
+      <c r="E87" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="G87" t="s">
+      <c r="G87" s="1" t="s">
         <v>222</v>
       </c>
-      <c r="H87" t="s">
+      <c r="H87" s="1" t="s">
         <v>220</v>
       </c>
-      <c r="I87" t="s">
+      <c r="I87" s="1" t="s">
         <v>221</v>
       </c>
-      <c r="J87" t="s">
+      <c r="J87" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="K87" t="s">
+      <c r="K87" s="1" t="s">
         <v>224</v>
       </c>
-      <c r="M87" t="s">
+      <c r="M87" s="1" t="s">
         <v>223</v>
       </c>
-      <c r="O87" t="s">
+      <c r="O87" s="1" t="s">
         <v>225</v>
       </c>
-      <c r="P87" t="s">
+      <c r="P87" s="1" t="s">
         <v>216</v>
       </c>
     </row>
